--- a/data/heroes ally.xlsx
+++ b/data/heroes ally.xlsx
@@ -1087,7 +1087,7 @@
         <v>2</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL4" s="3" t="n">
         <v>-6</v>
@@ -1739,7 +1739,7 @@
         <v>1</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL8" s="3" t="n">
         <v>-6</v>
@@ -2391,7 +2391,7 @@
         <v>-1</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AL12" s="3" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>1</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL13" s="3" t="n">
         <v>-6</v>
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AL14" s="3" t="n">
         <v>0</v>
@@ -3043,7 +3043,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL16" s="3" t="n">
         <v>-6</v>
@@ -3858,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AL21" s="3" t="n">
         <v>0</v>
@@ -4897,16 +4897,16 @@
         <v>2</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>-12</v>
@@ -4924,19 +4924,19 @@
         <v>1</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>-8</v>
@@ -4969,7 +4969,7 @@
         <v>0</v>
       </c>
       <c r="AA28" s="3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AB28" s="3" t="n">
         <v>-11</v>
@@ -4984,13 +4984,13 @@
         <v>1</v>
       </c>
       <c r="AF28" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AH28" s="3" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>0</v>
@@ -4999,7 +4999,7 @@
         <v>1</v>
       </c>
       <c r="AK28" s="3" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AL28" s="3" t="n">
         <v>1</v>
@@ -5008,31 +5008,31 @@
         <v>1</v>
       </c>
       <c r="AN28" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AP28" s="3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AQ28" s="3" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AR28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AS28" s="3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AT28" s="3" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AU28" s="3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AV28" s="3" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="AW28" s="3" t="n">
         <v>0</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AL32" s="3" t="n">
         <v>0</v>
@@ -5977,7 +5977,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AL34" s="3" t="n">
         <v>0</v>
@@ -6367,7 +6367,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>0</v>
@@ -6379,7 +6379,7 @@
         <v>-2</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>0</v>
@@ -6391,19 +6391,19 @@
         <v>-2</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="O37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q37" s="3" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
         <v>-1</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="V37" s="3" t="n">
         <v>0</v>
@@ -6451,13 +6451,13 @@
         <v>0</v>
       </c>
       <c r="AF37" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AG37" s="3" t="n">
         <v>-1</v>
       </c>
       <c r="AH37" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AI37" s="3" t="n">
         <v>0</v>
@@ -6469,22 +6469,22 @@
         <v>0</v>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM37" s="3" t="n">
         <v>-1</v>
       </c>
       <c r="AN37" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO37" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AP37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ37" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AR37" s="3" t="n">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>1</v>
       </c>
       <c r="AK38" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL38" s="3" t="n">
         <v>0</v>
@@ -6955,7 +6955,7 @@
         <v>2</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL40" s="3" t="n">
         <v>-6</v>
@@ -7118,7 +7118,7 @@
         <v>1</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL41" s="3" t="n">
         <v>-6</v>
@@ -7444,7 +7444,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="AL43" s="3" t="n">
         <v>0</v>
